--- a/artfynd/A 14554-2026 artfynd.xlsx
+++ b/artfynd/A 14554-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY122"/>
+  <dimension ref="A1:AZ122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14589145</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14589147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14589152</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14589157</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948654</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1422,6 +1452,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948655</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1547,6 +1582,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948656</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1672,6 +1712,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948657</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1797,6 +1842,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948658</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1922,6 +1972,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948659</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2047,6 +2102,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948660</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2172,6 +2232,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948662</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2297,6 +2362,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948663</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2422,6 +2492,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948676</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2547,6 +2622,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/14948677</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2700,6 +2780,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16589625</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2853,6 +2938,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16589626</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3006,6 +3096,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16589627</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3159,6 +3254,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16589628</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3312,6 +3412,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16589629</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3458,6 +3563,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520402</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3604,6 +3714,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520403</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3750,6 +3865,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520404</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3896,6 +4016,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520405</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4042,6 +4167,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520406</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4188,6 +4318,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520407</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4334,6 +4469,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520408</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4480,6 +4620,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520409</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4626,6 +4771,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61520410</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4762,6 +4912,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67444098</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4898,6 +5053,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67444099</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5034,6 +5194,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67444100</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5179,6 +5344,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916880</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5324,6 +5494,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916881</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5469,6 +5644,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916883</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5614,6 +5794,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916884</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5759,6 +5944,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916885</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5904,6 +6094,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916886</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6049,6 +6244,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916887</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6194,6 +6394,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916888</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6339,6 +6544,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916889</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6484,6 +6694,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916890</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6629,6 +6844,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69916891</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6774,6 +6994,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69917421</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6919,6 +7144,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181412</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7064,6 +7294,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181415</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7209,6 +7444,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181417</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7354,6 +7594,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181418</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7499,6 +7744,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181419</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7644,6 +7894,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181421</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7789,6 +8044,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181422</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7934,6 +8194,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80181423</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -8074,6 +8339,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143176</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8214,6 +8484,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143177</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8354,6 +8629,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143178</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8494,6 +8774,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143179</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8634,6 +8919,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143180</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8774,6 +9064,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143181</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8914,6 +9209,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143182</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -9054,6 +9354,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143183</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9194,6 +9499,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143184</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9334,6 +9644,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143185</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9474,6 +9789,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143186</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9614,6 +9934,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143187</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9754,6 +10079,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143188</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9894,6 +10224,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143189</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -10034,6 +10369,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143190</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -10174,6 +10514,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143191</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10314,6 +10659,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143192</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10454,6 +10804,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143193</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10594,6 +10949,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143194</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10734,6 +11094,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143196</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10874,6 +11239,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143197</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -11014,6 +11384,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143198</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -11154,6 +11529,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143200</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -11294,6 +11674,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143203</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11434,6 +11819,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88143204</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11554,6 +11944,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94146500</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11684,6 +12079,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94277634</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11814,6 +12214,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94277635</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11944,6 +12349,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94277636</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12087,6 +12497,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219920</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -12230,6 +12645,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219921</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12373,6 +12793,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219923</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12516,6 +12941,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219924</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12659,6 +13089,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219925</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12802,6 +13237,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219926</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12945,6 +13385,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219927</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -13088,6 +13533,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219928</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13231,6 +13681,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96219929</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -13366,6 +13821,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104177156</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -13506,6 +13966,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112645800</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -13646,6 +14111,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112645801</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -13786,6 +14256,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112645803</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13926,6 +14401,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112645804</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -14066,6 +14546,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112645805</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -14206,6 +14691,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112645806</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -14346,6 +14836,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617536</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -14486,6 +14981,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617537</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -14626,6 +15126,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617539</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14766,6 +15271,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617540</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -14906,6 +15416,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617541</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -15046,6 +15561,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617542</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -15186,6 +15706,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617543</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -15326,6 +15851,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617545</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -15466,6 +15996,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120617546</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -15606,6 +16141,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012810</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -15746,6 +16286,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012812</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -15886,6 +16431,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012813</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -16026,6 +16576,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012815</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -16166,6 +16721,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012816</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -16306,6 +16866,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012818</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -16446,6 +17011,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012820</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -16586,6 +17156,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012821</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -16726,6 +17301,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012823</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -16866,6 +17446,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012825</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -17006,6 +17591,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012826</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -17146,6 +17736,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012828</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -17286,6 +17881,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012829</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -17426,6 +18026,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129012830</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -17556,8 +18161,136 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/94277631</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>